--- a/source/Hoyeh Menu May 26 -UPDATED.xlsx
+++ b/source/Hoyeh Menu May 26 -UPDATED.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/chef_hoyeh_jrgroup_com_sg/Documents/Desktop/RWS Mob/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{29B8DDAB-B7B2-4575-AC21-864C4156FDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0482173D-6518-4340-B37D-223FB3717093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="529">
   <si>
     <t>Meal</t>
   </si>
@@ -1702,6 +1691,15 @@
   </si>
   <si>
     <t>Fried Chicken Wanton</t>
+  </si>
+  <si>
+    <t>4 x Salads (Honey Mustard and Vinaigrette)</t>
+  </si>
+  <si>
+    <t>4 x Salads (Caesar and Vinaigrette)</t>
+  </si>
+  <si>
+    <t>4 x Salads (Creamy Garlic Dressingand Vinaigrette)</t>
   </si>
 </sst>
 </file>
@@ -2533,6 +2531,30 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2542,34 +2564,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2907,15 +2905,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3331950C-5F09-41DF-8A79-5F2EED696A70}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -2926,7 +2924,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -2953,7 +2951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -2978,7 +2976,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -3007,7 +3005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="24" t="s">
         <v>9</v>
@@ -3034,7 +3032,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="26" t="s">
         <v>10</v>
@@ -3061,7 +3059,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="24" t="s">
         <v>23</v>
@@ -3088,7 +3086,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80"/>
       <c r="B8" s="29" t="s">
         <v>11</v>
@@ -3115,7 +3113,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -3144,7 +3142,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="82"/>
       <c r="B10" s="17" t="s">
         <v>43</v>
@@ -3171,9 +3169,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3198,9 +3196,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="19" t="s">
         <v>281</v>
       </c>
@@ -3223,9 +3221,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="66" t="s">
         <v>467</v>
       </c>
@@ -3248,9 +3246,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="19" t="s">
         <v>82</v>
       </c>
@@ -3273,9 +3271,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3298,9 +3296,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3323,22 +3321,22 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="82"/>
       <c r="B17" s="17" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>61</v>
+        <v>526</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>62</v>
+        <v>527</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>63</v>
+        <v>528</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -3350,7 +3348,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="82"/>
       <c r="B18" s="17" t="s">
         <v>13</v>
@@ -3377,7 +3375,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="83"/>
       <c r="B19" s="38" t="s">
         <v>60</v>
@@ -3404,8 +3402,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="88" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3433,8 +3431,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3460,9 +3458,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87"/>
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88"/>
+      <c r="B22" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3487,9 +3485,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87"/>
-      <c r="B23" s="85"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="31" t="s">
         <v>473</v>
       </c>
@@ -3512,9 +3510,9 @@
         <v>472</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87"/>
-      <c r="B24" s="85"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="31" t="s">
         <v>78</v>
       </c>
@@ -3537,9 +3535,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87"/>
-      <c r="B25" s="85"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="19" t="s">
         <v>314</v>
       </c>
@@ -3562,9 +3560,9 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
-      <c r="B26" s="85"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="19" t="s">
         <v>116</v>
       </c>
@@ -3587,9 +3585,9 @@
         <v>322</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
-      <c r="B27" s="86"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -3612,8 +3610,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -3639,8 +3637,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3666,8 +3664,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="89"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -3693,8 +3691,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3722,8 +3720,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3749,9 +3747,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3776,9 +3774,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="19" t="s">
         <v>281</v>
       </c>
@@ -3801,9 +3799,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="19" t="s">
         <v>82</v>
       </c>
@@ -3826,9 +3824,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3851,9 +3849,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3876,8 +3874,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -3903,8 +3901,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -3930,7 +3928,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="45" t="s">
         <v>14</v>
       </c>
@@ -3959,7 +3957,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -3988,7 +3986,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -3999,7 +3997,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="10"/>
@@ -4010,15 +4008,15 @@
       <c r="H43" s="11"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -4029,7 +4027,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -4040,7 +4038,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -4051,7 +4049,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -4062,7 +4060,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="10"/>
@@ -4073,12 +4071,12 @@
       <c r="H50" s="11"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="10"/>
@@ -4089,15 +4087,15 @@
       <c r="H52" s="11"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -4108,27 +4106,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -4139,7 +4137,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="10"/>
@@ -4150,15 +4148,15 @@
       <c r="H61" s="11"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -4169,7 +4167,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -4180,7 +4178,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -4191,7 +4189,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -4202,7 +4200,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -4213,7 +4211,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -4224,7 +4222,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -4235,7 +4233,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -4246,7 +4244,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="10"/>
@@ -4257,7 +4255,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -4268,7 +4266,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -4279,7 +4277,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -4290,7 +4288,7 @@
       <c r="H75" s="70"/>
       <c r="I75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="70"/>
@@ -4302,7 +4300,7 @@
       <c r="I76" s="70"/>
       <c r="J76" s="70"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -4313,7 +4311,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -4324,19 +4322,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
     </row>
@@ -4364,15 +4362,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF35105-E78C-446D-B499-ECA475F17C6E}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4383,7 +4381,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -4410,9 +4408,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
       <c r="C3" s="68">
         <v>46153</v>
       </c>
@@ -4435,7 +4433,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -4464,7 +4462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -4491,7 +4489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -4518,7 +4516,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -4545,7 +4543,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -4572,7 +4570,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -4601,7 +4599,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="82"/>
       <c r="B10" s="63" t="s">
         <v>43</v>
@@ -4628,9 +4626,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4655,9 +4653,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="94"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>102</v>
       </c>
@@ -4680,9 +4678,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="94"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="19" t="s">
         <v>332</v>
       </c>
@@ -4705,9 +4703,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="94"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>105</v>
       </c>
@@ -4730,9 +4728,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="94"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>109</v>
       </c>
@@ -4755,9 +4753,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="95"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>235</v>
       </c>
@@ -4780,7 +4778,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="82"/>
       <c r="B17" s="63" t="s">
         <v>59</v>
@@ -4807,7 +4805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="82"/>
       <c r="B18" s="63" t="s">
         <v>13</v>
@@ -4834,7 +4832,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="83"/>
       <c r="B19" s="64" t="s">
         <v>60</v>
@@ -4861,8 +4859,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -4890,8 +4888,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -4917,9 +4915,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87"/>
-      <c r="B22" s="93" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4944,9 +4942,9 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87"/>
-      <c r="B23" s="94"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="19" t="s">
         <v>112</v>
       </c>
@@ -4969,9 +4967,9 @@
         <v>365</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87"/>
-      <c r="B24" s="94"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="19" t="s">
         <v>353</v>
       </c>
@@ -4994,9 +4992,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87"/>
-      <c r="B25" s="94"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>237</v>
       </c>
@@ -5019,9 +5017,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
-      <c r="B26" s="94"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="66" t="s">
         <v>236</v>
       </c>
@@ -5044,9 +5042,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
-      <c r="B27" s="95"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -5069,8 +5067,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -5096,8 +5094,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -5123,8 +5121,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="89"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -5150,8 +5148,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="62" t="s">
@@ -5179,8 +5177,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="91"/>
       <c r="B32" s="63" t="s">
         <v>43</v>
       </c>
@@ -5206,9 +5204,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="90"/>
-      <c r="B33" s="93" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="91"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5233,9 +5231,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="90"/>
-      <c r="B34" s="94"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="91"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>102</v>
       </c>
@@ -5258,9 +5256,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="90"/>
-      <c r="B35" s="94"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="91"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>105</v>
       </c>
@@ -5283,9 +5281,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90"/>
-      <c r="B36" s="94"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="91"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>109</v>
       </c>
@@ -5308,9 +5306,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="90"/>
-      <c r="B37" s="94"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="91"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>235</v>
       </c>
@@ -5333,8 +5331,8 @@
         <v>346</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="91"/>
       <c r="B38" s="63" t="s">
         <v>59</v>
       </c>
@@ -5360,8 +5358,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="91"/>
       <c r="B39" s="63" t="s">
         <v>13</v>
       </c>
@@ -5387,8 +5385,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="91"/>
       <c r="B40" s="63" t="s">
         <v>60</v>
       </c>
@@ -5414,7 +5412,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -5443,7 +5441,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -5454,7 +5452,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="10"/>
@@ -5465,15 +5463,15 @@
       <c r="H43" s="11"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -5484,7 +5482,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -5495,7 +5493,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -5506,7 +5504,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -5517,7 +5515,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="10"/>
@@ -5528,12 +5526,12 @@
       <c r="H50" s="11"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="10"/>
@@ -5544,15 +5542,15 @@
       <c r="H52" s="11"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -5563,27 +5561,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -5594,7 +5592,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="10"/>
@@ -5605,15 +5603,15 @@
       <c r="H61" s="11"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -5624,7 +5622,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -5635,7 +5633,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -5646,7 +5644,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -5657,7 +5655,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -5668,7 +5666,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -5679,7 +5677,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -5690,7 +5688,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -5701,7 +5699,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="10"/>
@@ -5712,7 +5710,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -5723,7 +5721,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -5734,7 +5732,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -5745,7 +5743,7 @@
       <c r="H75" s="70"/>
       <c r="I75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="70"/>
@@ -5757,7 +5755,7 @@
       <c r="I76" s="70"/>
       <c r="J76" s="70"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -5768,7 +5766,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -5779,19 +5777,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
     </row>
@@ -5819,15 +5817,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFDDF52-516B-4631-A9D2-1246E2DB53C6}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -5838,7 +5836,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -5865,7 +5863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -5890,7 +5888,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -5919,7 +5917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -5946,7 +5944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -5973,7 +5971,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -6000,7 +5998,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -6027,7 +6025,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -6056,7 +6054,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="82"/>
       <c r="B10" s="17" t="s">
         <v>43</v>
@@ -6083,9 +6081,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6110,9 +6108,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="31" t="s">
         <v>373</v>
       </c>
@@ -6135,9 +6133,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="31" t="s">
         <v>379</v>
       </c>
@@ -6160,9 +6158,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="31" t="s">
         <v>390</v>
       </c>
@@ -6185,9 +6183,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="31" t="s">
         <v>395</v>
       </c>
@@ -6210,9 +6208,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="31" t="s">
         <v>142</v>
       </c>
@@ -6235,7 +6233,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="82"/>
       <c r="B17" s="17" t="s">
         <v>59</v>
@@ -6262,7 +6260,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="82"/>
       <c r="B18" s="17" t="s">
         <v>13</v>
@@ -6289,7 +6287,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="83"/>
       <c r="B19" s="38" t="s">
         <v>60</v>
@@ -6316,8 +6314,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6345,8 +6343,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6372,9 +6370,9 @@
         <v>411</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87"/>
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88"/>
+      <c r="B22" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6399,9 +6397,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87"/>
-      <c r="B23" s="85"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="31" t="s">
         <v>148</v>
       </c>
@@ -6424,9 +6422,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87"/>
-      <c r="B24" s="85"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6449,9 +6447,9 @@
         <v>508</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87"/>
-      <c r="B25" s="85"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="31" t="s">
         <v>415</v>
       </c>
@@ -6474,9 +6472,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
-      <c r="B26" s="85"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6499,9 +6497,9 @@
         <v>419</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
-      <c r="B27" s="86"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="31" t="s">
         <v>369</v>
       </c>
@@ -6524,8 +6522,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -6551,8 +6549,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6578,8 +6576,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="89"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -6605,8 +6603,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6634,8 +6632,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6661,9 +6659,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6688,9 +6686,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="31" t="s">
         <v>373</v>
       </c>
@@ -6713,9 +6711,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="31" t="s">
         <v>390</v>
       </c>
@@ -6738,9 +6736,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="31" t="s">
         <v>395</v>
       </c>
@@ -6763,9 +6761,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="31" t="s">
         <v>142</v>
       </c>
@@ -6788,8 +6786,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -6815,8 +6813,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6842,8 +6840,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="91"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -6869,7 +6867,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -6898,7 +6896,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -6909,15 +6907,15 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -6928,7 +6926,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -6939,7 +6937,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -6950,7 +6948,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="10"/>
@@ -6961,7 +6959,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -6972,12 +6970,12 @@
       <c r="H49" s="11"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="10"/>
@@ -6988,15 +6986,15 @@
       <c r="H51" s="11"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -7007,27 +7005,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="10"/>
@@ -7038,7 +7036,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -7049,15 +7047,15 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="10"/>
@@ -7068,7 +7066,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -7079,7 +7077,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -7090,7 +7088,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -7101,7 +7099,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -7112,7 +7110,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -7123,7 +7121,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -7134,7 +7132,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -7145,7 +7143,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -7156,7 +7154,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -7167,7 +7165,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -7178,7 +7176,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="70"/>
@@ -7189,7 +7187,7 @@
       <c r="H74" s="70"/>
       <c r="I74" s="70"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -7201,7 +7199,7 @@
       <c r="I75" s="70"/>
       <c r="J75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -7212,7 +7210,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -7223,19 +7221,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
     </row>
@@ -7263,15 +7261,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29988196-DFEB-46AE-A95C-9191B0B4EB55}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -7282,7 +7280,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -7309,7 +7307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -7334,7 +7332,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -7363,7 +7361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -7390,7 +7388,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -7417,7 +7415,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -7444,7 +7442,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -7471,7 +7469,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -7500,7 +7498,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="82"/>
       <c r="B10" s="63" t="s">
         <v>43</v>
@@ -7527,9 +7525,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -7554,9 +7552,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="94"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>168</v>
       </c>
@@ -7579,9 +7577,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="94"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="19" t="s">
         <v>434</v>
       </c>
@@ -7604,9 +7602,9 @@
         <v>412</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="94"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>251</v>
       </c>
@@ -7629,9 +7627,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="94"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>250</v>
       </c>
@@ -7654,9 +7652,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="95"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>502</v>
       </c>
@@ -7679,7 +7677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="82"/>
       <c r="B17" s="63" t="s">
         <v>59</v>
@@ -7706,7 +7704,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="82"/>
       <c r="B18" s="63" t="s">
         <v>13</v>
@@ -7733,7 +7731,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="83"/>
       <c r="B19" s="64" t="s">
         <v>60</v>
@@ -7760,8 +7758,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -7789,8 +7787,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -7816,9 +7814,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87"/>
-      <c r="B22" s="93" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="88"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7843,9 +7841,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87"/>
-      <c r="B23" s="94"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="19" t="s">
         <v>175</v>
       </c>
@@ -7868,9 +7866,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87"/>
-      <c r="B24" s="94"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="88"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="19" t="s">
         <v>179</v>
       </c>
@@ -7893,9 +7891,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87"/>
-      <c r="B25" s="94"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="88"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>105</v>
       </c>
@@ -7918,9 +7916,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
-      <c r="B26" s="94"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="88"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="19" t="s">
         <v>260</v>
       </c>
@@ -7943,9 +7941,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
-      <c r="B27" s="95"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>455</v>
       </c>
@@ -7968,8 +7966,8 @@
         <v>323</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="88"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -7995,8 +7993,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="88"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -8022,8 +8020,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="89"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -8049,8 +8047,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8078,8 +8076,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8105,9 +8103,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -8132,9 +8130,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="19" t="s">
         <v>168</v>
       </c>
@@ -8157,9 +8155,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="19" t="s">
         <v>251</v>
       </c>
@@ -8182,9 +8180,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="19" t="s">
         <v>250</v>
       </c>
@@ -8207,9 +8205,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="19" t="s">
         <v>502</v>
       </c>
@@ -8232,8 +8230,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -8259,8 +8257,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8286,8 +8284,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="91"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -8313,7 +8311,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -8342,7 +8340,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -8353,15 +8351,15 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -8372,7 +8370,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -8383,7 +8381,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -8394,7 +8392,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="10"/>
@@ -8405,7 +8403,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -8416,12 +8414,12 @@
       <c r="H49" s="11"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="10"/>
@@ -8432,15 +8430,15 @@
       <c r="H51" s="11"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -8451,27 +8449,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="10"/>
@@ -8482,7 +8480,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -8493,15 +8491,15 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="10"/>
@@ -8512,7 +8510,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -8523,7 +8521,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -8534,7 +8532,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -8545,7 +8543,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -8556,7 +8554,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -8567,7 +8565,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -8578,7 +8576,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -8589,7 +8587,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -8600,7 +8598,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -8611,7 +8609,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -8622,7 +8620,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="70"/>
@@ -8633,7 +8631,7 @@
       <c r="H74" s="70"/>
       <c r="I74" s="70"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -8645,7 +8643,7 @@
       <c r="I75" s="70"/>
       <c r="J75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -8656,7 +8654,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -8667,19 +8665,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
     </row>

--- a/source/Hoyeh Menu May 26 -UPDATED.xlsx
+++ b/source/Hoyeh Menu May 26 -UPDATED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0482173D-6518-4340-B37D-223FB3717093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8682BE1F-80CB-46F3-A2C8-BA58637FD928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -2531,6 +2531,33 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2541,33 +2568,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3198,7 +3198,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="93"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>281</v>
       </c>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="93"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="66" t="s">
         <v>467</v>
       </c>
@@ -3248,7 +3248,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="93"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>82</v>
       </c>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="93"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="94"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3403,7 +3403,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3432,7 +3432,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3459,8 +3459,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3486,8 +3486,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="93"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="31" t="s">
         <v>473</v>
       </c>
@@ -3511,8 +3511,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="93"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="31" t="s">
         <v>78</v>
       </c>
@@ -3536,8 +3536,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>314</v>
       </c>
@@ -3561,8 +3561,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="93"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="19" t="s">
         <v>116</v>
       </c>
@@ -3586,8 +3586,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="94"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -3611,7 +3611,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -3638,7 +3638,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3665,7 +3665,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -3692,7 +3692,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3721,7 +3721,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3748,8 +3748,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3775,8 +3775,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>281</v>
       </c>
@@ -3800,8 +3800,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>82</v>
       </c>
@@ -3825,8 +3825,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3850,8 +3850,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3875,7 +3875,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -3902,7 +3902,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -4409,8 +4409,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
       <c r="C3" s="68">
         <v>46153</v>
       </c>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4655,7 +4655,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="19" t="s">
         <v>102</v>
       </c>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="19" t="s">
         <v>332</v>
       </c>
@@ -4705,7 +4705,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="19" t="s">
         <v>105</v>
       </c>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="19" t="s">
         <v>109</v>
       </c>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="19" t="s">
         <v>235</v>
       </c>
@@ -4784,16 +4784,16 @@
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>61</v>
+        <v>526</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>62</v>
+        <v>527</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>63</v>
+        <v>528</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -4860,7 +4860,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -4889,7 +4889,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -4916,8 +4916,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4943,8 +4943,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="19" t="s">
         <v>112</v>
       </c>
@@ -4968,8 +4968,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="85"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="94"/>
       <c r="C24" s="19" t="s">
         <v>353</v>
       </c>
@@ -4993,8 +4993,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="85"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="19" t="s">
         <v>237</v>
       </c>
@@ -5018,8 +5018,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="66" t="s">
         <v>236</v>
       </c>
@@ -5043,8 +5043,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -5068,7 +5068,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -5095,7 +5095,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -5122,7 +5122,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -5149,7 +5149,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="62" t="s">
@@ -5178,7 +5178,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="63" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5205,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="84" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5232,8 +5232,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
-      <c r="B34" s="85"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="94"/>
       <c r="C34" s="19" t="s">
         <v>102</v>
       </c>
@@ -5257,8 +5257,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="85"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="19" t="s">
         <v>105</v>
       </c>
@@ -5282,8 +5282,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
-      <c r="B36" s="85"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="19" t="s">
         <v>109</v>
       </c>
@@ -5307,8 +5307,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
-      <c r="B37" s="85"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="94"/>
       <c r="C37" s="19" t="s">
         <v>235</v>
       </c>
@@ -5332,7 +5332,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="63" t="s">
         <v>59</v>
       </c>
@@ -5359,7 +5359,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="63" t="s">
         <v>13</v>
       </c>
@@ -5386,7 +5386,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="63" t="s">
         <v>60</v>
       </c>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6110,7 +6110,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="93"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="31" t="s">
         <v>373</v>
       </c>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="93"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="31" t="s">
         <v>379</v>
       </c>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="93"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="31" t="s">
         <v>390</v>
       </c>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="93"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="31" t="s">
         <v>395</v>
       </c>
@@ -6210,7 +6210,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="94"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="31" t="s">
         <v>142</v>
       </c>
@@ -6315,7 +6315,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6344,7 +6344,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6371,8 +6371,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6398,8 +6398,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="93"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="31" t="s">
         <v>148</v>
       </c>
@@ -6423,8 +6423,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="93"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6448,8 +6448,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="31" t="s">
         <v>415</v>
       </c>
@@ -6473,8 +6473,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="93"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6498,8 +6498,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="94"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="31" t="s">
         <v>369</v>
       </c>
@@ -6523,21 +6523,21 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>61</v>
+        <v>526</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>62</v>
+        <v>527</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>63</v>
+        <v>528</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>65</v>
@@ -6550,7 +6550,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6577,7 +6577,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -6604,7 +6604,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6633,7 +6633,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6660,8 +6660,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6687,8 +6687,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="31" t="s">
         <v>373</v>
       </c>
@@ -6712,8 +6712,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="31" t="s">
         <v>390</v>
       </c>
@@ -6737,8 +6737,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="31" t="s">
         <v>395</v>
       </c>
@@ -6762,8 +6762,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="31" t="s">
         <v>142</v>
       </c>
@@ -6787,7 +6787,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -6814,7 +6814,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6841,7 +6841,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -7527,7 +7527,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -7554,7 +7554,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="19" t="s">
         <v>168</v>
       </c>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="19" t="s">
         <v>434</v>
       </c>
@@ -7604,7 +7604,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="19" t="s">
         <v>251</v>
       </c>
@@ -7629,7 +7629,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="19" t="s">
         <v>250</v>
       </c>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="19" t="s">
         <v>502</v>
       </c>
@@ -7683,16 +7683,16 @@
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>61</v>
+        <v>526</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>62</v>
+        <v>527</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>63</v>
+        <v>528</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -7759,7 +7759,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -7788,7 +7788,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -7815,8 +7815,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7842,8 +7842,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="19" t="s">
         <v>175</v>
       </c>
@@ -7867,8 +7867,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="85"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="94"/>
       <c r="C24" s="19" t="s">
         <v>179</v>
       </c>
@@ -7892,8 +7892,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="85"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="19" t="s">
         <v>105</v>
       </c>
@@ -7917,8 +7917,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="19" t="s">
         <v>260</v>
       </c>
@@ -7942,8 +7942,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="19" t="s">
         <v>455</v>
       </c>
@@ -7967,7 +7967,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -7994,7 +7994,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -8021,7 +8021,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -8048,7 +8048,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8077,7 +8077,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8104,8 +8104,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -8131,8 +8131,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>168</v>
       </c>
@@ -8156,8 +8156,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>251</v>
       </c>
@@ -8181,8 +8181,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>250</v>
       </c>
@@ -8206,8 +8206,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>502</v>
       </c>
@@ -8231,7 +8231,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -8258,7 +8258,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8285,7 +8285,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>

--- a/source/Hoyeh Menu May 26 -UPDATED.xlsx
+++ b/source/Hoyeh Menu May 26 -UPDATED.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/om_hoyeh_jrgroup_com_sg/Documents/Desktop/menu-rws hoyeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8682BE1F-80CB-46F3-A2C8-BA58637FD928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{29B8DDAB-B7B2-4575-AC21-864C4156FDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A8453B-D9D2-4C70-A1AE-BB395E853199}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="527">
   <si>
     <t>Meal</t>
   </si>
@@ -1693,13 +1702,7 @@
     <t>Fried Chicken Wanton</t>
   </si>
   <si>
-    <t>4 x Salads (Honey Mustard and Vinaigrette)</t>
-  </si>
-  <si>
-    <t>4 x Salads (Caesar and Vinaigrette)</t>
-  </si>
-  <si>
-    <t>4 x Salads (Creamy Garlic Dressingand Vinaigrette)</t>
+    <t>Teriyaki Fish W/ garlic Rice</t>
   </si>
 </sst>
 </file>
@@ -2531,6 +2534,30 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2540,34 +2567,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2905,15 +2908,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3331950C-5F09-41DF-8A79-5F2EED696A70}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -2924,7 +2927,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -2951,7 +2954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -2976,7 +2979,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -3005,7 +3008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="79"/>
       <c r="B5" s="24" t="s">
         <v>9</v>
@@ -3032,7 +3035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="79"/>
       <c r="B6" s="26" t="s">
         <v>10</v>
@@ -3059,7 +3062,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="79"/>
       <c r="B7" s="24" t="s">
         <v>23</v>
@@ -3086,7 +3089,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="80"/>
       <c r="B8" s="29" t="s">
         <v>11</v>
@@ -3113,7 +3116,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>483</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>17</v>
+        <v>372</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>277</v>
@@ -3142,7 +3145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="82"/>
       <c r="B10" s="17" t="s">
         <v>43</v>
@@ -3157,7 +3160,7 @@
         <v>221</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>278</v>
+        <v>526</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>514</v>
@@ -3169,9 +3172,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3196,9 +3199,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="19" t="s">
         <v>281</v>
       </c>
@@ -3221,9 +3224,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="66" t="s">
         <v>467</v>
       </c>
@@ -3246,9 +3249,9 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="19" t="s">
         <v>82</v>
       </c>
@@ -3271,9 +3274,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3296,9 +3299,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3321,22 +3324,22 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="82"/>
       <c r="B17" s="17" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>527</v>
+        <v>62</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -3348,7 +3351,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="82"/>
       <c r="B18" s="17" t="s">
         <v>13</v>
@@ -3375,7 +3378,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="38" t="s">
         <v>60</v>
@@ -3402,8 +3405,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="88" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3431,8 +3434,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="88"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3458,9 +3461,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="88"/>
+      <c r="B22" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3485,9 +3488,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="85"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="31" t="s">
         <v>473</v>
       </c>
@@ -3510,9 +3513,9 @@
         <v>472</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="85"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="88"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="31" t="s">
         <v>78</v>
       </c>
@@ -3535,9 +3538,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="85"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="88"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="19" t="s">
         <v>314</v>
       </c>
@@ -3560,9 +3563,9 @@
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="85"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="88"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="19" t="s">
         <v>116</v>
       </c>
@@ -3585,9 +3588,9 @@
         <v>322</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="86"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="88"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -3610,8 +3613,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="88"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -3637,8 +3640,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="88"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3664,8 +3667,8 @@
         <v>299</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="89"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -3691,8 +3694,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3720,8 +3723,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3747,9 +3750,9 @@
         <v>279</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3774,9 +3777,9 @@
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="19" t="s">
         <v>281</v>
       </c>
@@ -3799,9 +3802,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="19" t="s">
         <v>82</v>
       </c>
@@ -3824,9 +3827,9 @@
         <v>292</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3849,9 +3852,9 @@
         <v>293</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3874,8 +3877,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -3901,8 +3904,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="45" t="s">
         <v>14</v>
       </c>
@@ -3957,7 +3960,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -3986,7 +3989,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -3997,7 +4000,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="10"/>
@@ -4008,15 +4011,15 @@
       <c r="H43" s="11"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -4027,7 +4030,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -4038,7 +4041,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -4049,7 +4052,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -4060,7 +4063,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="10"/>
@@ -4071,12 +4074,12 @@
       <c r="H50" s="11"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="10"/>
@@ -4087,15 +4090,15 @@
       <c r="H52" s="11"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -4106,27 +4109,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -4137,7 +4140,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="10"/>
@@ -4148,15 +4151,15 @@
       <c r="H61" s="11"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -4167,7 +4170,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -4178,7 +4181,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -4189,7 +4192,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -4200,7 +4203,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -4211,7 +4214,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -4222,7 +4225,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -4233,7 +4236,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -4244,7 +4247,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="10"/>
@@ -4255,7 +4258,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -4266,7 +4269,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -4277,7 +4280,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -4288,7 +4291,7 @@
       <c r="H75" s="70"/>
       <c r="I75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="70"/>
@@ -4300,7 +4303,7 @@
       <c r="I76" s="70"/>
       <c r="J76" s="70"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -4311,7 +4314,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -4322,19 +4325,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
     </row>
@@ -4362,15 +4365,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF35105-E78C-446D-B499-ECA475F17C6E}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -4381,7 +4384,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -4408,9 +4411,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
       <c r="C3" s="68">
         <v>46153</v>
       </c>
@@ -4433,7 +4436,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -4462,7 +4465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -4489,7 +4492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -4516,7 +4519,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -4543,7 +4546,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -4570,7 +4573,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -4599,7 +4602,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="82"/>
       <c r="B10" s="63" t="s">
         <v>43</v>
@@ -4626,9 +4629,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4653,9 +4656,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="94"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>102</v>
       </c>
@@ -4678,9 +4681,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="94"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="19" t="s">
         <v>332</v>
       </c>
@@ -4703,9 +4706,9 @@
         <v>342</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="94"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>105</v>
       </c>
@@ -4728,9 +4731,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="94"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>109</v>
       </c>
@@ -4753,9 +4756,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="95"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>235</v>
       </c>
@@ -4778,22 +4781,22 @@
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="82"/>
       <c r="B17" s="63" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>527</v>
+        <v>62</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -4805,7 +4808,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="82"/>
       <c r="B18" s="63" t="s">
         <v>13</v>
@@ -4832,7 +4835,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="64" t="s">
         <v>60</v>
@@ -4859,8 +4862,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -4888,8 +4891,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="88"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -4915,9 +4918,9 @@
         <v>350</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="93" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="88"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4942,9 +4945,9 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="94"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="19" t="s">
         <v>112</v>
       </c>
@@ -4967,9 +4970,9 @@
         <v>365</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="94"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="88"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="19" t="s">
         <v>353</v>
       </c>
@@ -4992,9 +4995,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="94"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="88"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>237</v>
       </c>
@@ -5017,9 +5020,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="94"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="88"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="66" t="s">
         <v>236</v>
       </c>
@@ -5042,9 +5045,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="95"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="88"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -5067,8 +5070,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="88"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -5094,8 +5097,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="88"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -5121,8 +5124,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="89"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -5148,8 +5151,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="62" t="s">
@@ -5177,8 +5180,8 @@
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
       <c r="B32" s="63" t="s">
         <v>43</v>
       </c>
@@ -5204,9 +5207,9 @@
         <v>371</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="90"/>
-      <c r="B33" s="93" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5231,9 +5234,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="90"/>
-      <c r="B34" s="94"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="91"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>102</v>
       </c>
@@ -5256,9 +5259,9 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="90"/>
-      <c r="B35" s="94"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="91"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>105</v>
       </c>
@@ -5281,9 +5284,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="90"/>
-      <c r="B36" s="94"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="91"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>109</v>
       </c>
@@ -5306,9 +5309,9 @@
         <v>287</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
-      <c r="B37" s="94"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="91"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>235</v>
       </c>
@@ -5331,8 +5334,8 @@
         <v>346</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="91"/>
       <c r="B38" s="63" t="s">
         <v>59</v>
       </c>
@@ -5358,8 +5361,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="91"/>
       <c r="B39" s="63" t="s">
         <v>13</v>
       </c>
@@ -5385,8 +5388,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="91"/>
       <c r="B40" s="63" t="s">
         <v>60</v>
       </c>
@@ -5412,7 +5415,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -5441,7 +5444,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -5452,7 +5455,7 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="10"/>
@@ -5463,15 +5466,15 @@
       <c r="H43" s="11"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -5482,7 +5485,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -5493,7 +5496,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -5504,7 +5507,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -5515,7 +5518,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="10"/>
@@ -5526,12 +5529,12 @@
       <c r="H50" s="11"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="10"/>
@@ -5542,15 +5545,15 @@
       <c r="H52" s="11"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -5561,27 +5564,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -5592,7 +5595,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="10"/>
@@ -5603,15 +5606,15 @@
       <c r="H61" s="11"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -5622,7 +5625,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -5633,7 +5636,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -5644,7 +5647,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -5655,7 +5658,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -5666,7 +5669,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -5677,7 +5680,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -5688,7 +5691,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -5699,7 +5702,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="10"/>
@@ -5710,7 +5713,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -5721,7 +5724,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -5732,7 +5735,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -5743,7 +5746,7 @@
       <c r="H75" s="70"/>
       <c r="I75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="70"/>
@@ -5755,7 +5758,7 @@
       <c r="I76" s="70"/>
       <c r="J76" s="70"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -5766,7 +5769,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -5777,19 +5780,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
     </row>
@@ -5817,15 +5820,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFDDF52-516B-4631-A9D2-1246E2DB53C6}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -5836,7 +5839,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -5863,7 +5866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -5888,7 +5891,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -5917,7 +5920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -5944,7 +5947,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -5971,7 +5974,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -5998,7 +6001,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -6025,7 +6028,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -6054,7 +6057,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="82"/>
       <c r="B10" s="17" t="s">
         <v>43</v>
@@ -6081,9 +6084,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6108,9 +6111,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="31" t="s">
         <v>373</v>
       </c>
@@ -6133,9 +6136,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="31" t="s">
         <v>379</v>
       </c>
@@ -6158,9 +6161,9 @@
         <v>389</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="31" t="s">
         <v>390</v>
       </c>
@@ -6183,9 +6186,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="31" t="s">
         <v>395</v>
       </c>
@@ -6208,9 +6211,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="94"/>
       <c r="C16" s="31" t="s">
         <v>142</v>
       </c>
@@ -6233,7 +6236,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="82"/>
       <c r="B17" s="17" t="s">
         <v>59</v>
@@ -6260,7 +6263,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="82"/>
       <c r="B18" s="17" t="s">
         <v>13</v>
@@ -6287,7 +6290,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="38" t="s">
         <v>60</v>
@@ -6314,8 +6317,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6343,8 +6346,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="88"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6370,9 +6373,9 @@
         <v>411</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="88"/>
+      <c r="B22" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6397,9 +6400,9 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="85"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="31" t="s">
         <v>148</v>
       </c>
@@ -6422,9 +6425,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="85"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="88"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6447,9 +6450,9 @@
         <v>508</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="85"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="88"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="31" t="s">
         <v>415</v>
       </c>
@@ -6472,9 +6475,9 @@
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="85"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="88"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6497,9 +6500,9 @@
         <v>419</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="86"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="88"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="31" t="s">
         <v>369</v>
       </c>
@@ -6522,22 +6525,22 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="88"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>527</v>
+        <v>62</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>65</v>
@@ -6549,8 +6552,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="88"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6576,8 +6579,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="89"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -6603,8 +6606,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6632,8 +6635,8 @@
         <v>375</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6659,9 +6662,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6686,9 +6689,9 @@
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="31" t="s">
         <v>373</v>
       </c>
@@ -6711,9 +6714,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="31" t="s">
         <v>390</v>
       </c>
@@ -6736,9 +6739,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="31" t="s">
         <v>395</v>
       </c>
@@ -6761,9 +6764,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="31" t="s">
         <v>142</v>
       </c>
@@ -6786,8 +6789,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -6813,8 +6816,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6840,8 +6843,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="91"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -6867,7 +6870,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -6896,7 +6899,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -6907,15 +6910,15 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -6926,7 +6929,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -6937,7 +6940,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -6948,7 +6951,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="10"/>
@@ -6959,7 +6962,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -6970,12 +6973,12 @@
       <c r="H49" s="11"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="10"/>
@@ -6986,15 +6989,15 @@
       <c r="H51" s="11"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -7005,27 +7008,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="10"/>
@@ -7036,7 +7039,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -7047,15 +7050,15 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="10"/>
@@ -7066,7 +7069,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -7077,7 +7080,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -7088,7 +7091,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -7099,7 +7102,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -7110,7 +7113,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -7121,7 +7124,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -7132,7 +7135,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -7143,7 +7146,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -7154,7 +7157,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -7165,7 +7168,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -7176,7 +7179,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="70"/>
@@ -7187,7 +7190,7 @@
       <c r="H74" s="70"/>
       <c r="I74" s="70"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -7199,7 +7202,7 @@
       <c r="I75" s="70"/>
       <c r="J75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -7210,7 +7213,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -7221,19 +7224,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
     </row>
@@ -7261,15 +7264,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29988196-DFEB-46AE-A95C-9191B0B4EB55}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.44140625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="47.77734375" style="14" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.453125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="71"/>
       <c r="B1" s="72"/>
       <c r="C1" s="72"/>
@@ -7280,7 +7283,7 @@
       <c r="H1" s="72"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
@@ -7307,7 +7310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="76"/>
       <c r="B3" s="77"/>
       <c r="C3" s="3">
@@ -7332,7 +7335,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
         <v>8</v>
       </c>
@@ -7361,7 +7364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="79"/>
       <c r="B5" s="50" t="s">
         <v>9</v>
@@ -7388,7 +7391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="79"/>
       <c r="B6" s="51" t="s">
         <v>10</v>
@@ -7415,7 +7418,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="79"/>
       <c r="B7" s="50" t="s">
         <v>23</v>
@@ -7442,7 +7445,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="80"/>
       <c r="B8" s="52" t="s">
         <v>11</v>
@@ -7469,7 +7472,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="81" t="s">
         <v>12</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="82"/>
       <c r="B10" s="63" t="s">
         <v>43</v>
@@ -7525,9 +7528,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -7552,9 +7555,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="94"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>168</v>
       </c>
@@ -7577,9 +7580,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="94"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="19" t="s">
         <v>434</v>
       </c>
@@ -7602,9 +7605,9 @@
         <v>412</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="94"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>251</v>
       </c>
@@ -7627,9 +7630,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="94"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>250</v>
       </c>
@@ -7652,9 +7655,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="95"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>502</v>
       </c>
@@ -7677,22 +7680,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="82"/>
       <c r="B17" s="63" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>527</v>
+        <v>62</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>528</v>
+        <v>63</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>65</v>
@@ -7704,7 +7707,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="82"/>
       <c r="B18" s="63" t="s">
         <v>13</v>
@@ -7731,7 +7734,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="64" t="s">
         <v>60</v>
@@ -7758,8 +7761,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -7787,8 +7790,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="88"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -7814,9 +7817,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="93" t="s">
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="88"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7841,9 +7844,9 @@
         <v>269</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="94"/>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="88"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="19" t="s">
         <v>175</v>
       </c>
@@ -7866,9 +7869,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="94"/>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="88"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="19" t="s">
         <v>179</v>
       </c>
@@ -7891,9 +7894,9 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="94"/>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="88"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>105</v>
       </c>
@@ -7916,9 +7919,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="94"/>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="88"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="19" t="s">
         <v>260</v>
       </c>
@@ -7941,9 +7944,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="95"/>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="88"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>455</v>
       </c>
@@ -7966,8 +7969,8 @@
         <v>323</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="88"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -7993,8 +7996,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="88"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -8020,8 +8023,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="88"/>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="89"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -8047,8 +8050,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="89" t="s">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8076,8 +8079,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="90"/>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="91"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8103,9 +8106,9 @@
         <v>523</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="90"/>
-      <c r="B33" s="84" t="s">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="91"/>
+      <c r="B33" s="92" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -8130,9 +8133,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="90"/>
-      <c r="B34" s="85"/>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="19" t="s">
         <v>168</v>
       </c>
@@ -8155,9 +8158,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="90"/>
-      <c r="B35" s="85"/>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="19" t="s">
         <v>251</v>
       </c>
@@ -8180,9 +8183,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="90"/>
-      <c r="B36" s="85"/>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
       <c r="C36" s="19" t="s">
         <v>250</v>
       </c>
@@ -8205,9 +8208,9 @@
         <v>253</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
-      <c r="B37" s="85"/>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="91"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="19" t="s">
         <v>502</v>
       </c>
@@ -8230,8 +8233,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="90"/>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="91"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -8257,8 +8260,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="90"/>
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="91"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8284,8 +8287,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="90"/>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="91"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -8311,7 +8314,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="45" t="s">
         <v>14</v>
       </c>
@@ -8340,7 +8343,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="10"/>
@@ -8351,15 +8354,15 @@
       <c r="H42" s="11"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -8370,7 +8373,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -8381,7 +8384,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -8392,7 +8395,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="10"/>
@@ -8403,7 +8406,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="10"/>
@@ -8414,12 +8417,12 @@
       <c r="H49" s="11"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="10"/>
@@ -8430,15 +8433,15 @@
       <c r="H51" s="11"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -8449,27 +8452,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="10"/>
@@ -8480,7 +8483,7 @@
       <c r="H59" s="11"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="10"/>
@@ -8491,15 +8494,15 @@
       <c r="H60" s="11"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="10"/>
@@ -8510,7 +8513,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="10"/>
@@ -8521,7 +8524,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="10"/>
@@ -8532,7 +8535,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="10"/>
@@ -8543,7 +8546,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="10"/>
@@ -8554,7 +8557,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="10"/>
@@ -8565,7 +8568,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="10"/>
@@ -8576,7 +8579,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="10"/>
@@ -8587,7 +8590,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="10"/>
@@ -8598,7 +8601,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -8609,7 +8612,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -8620,7 +8623,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="70"/>
@@ -8631,7 +8634,7 @@
       <c r="H74" s="70"/>
       <c r="I74" s="70"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="70"/>
@@ -8643,7 +8646,7 @@
       <c r="I75" s="70"/>
       <c r="J75" s="70"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -8654,7 +8657,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -8665,19 +8668,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
     </row>

--- a/source/Hoyeh Menu May 26 -UPDATED.xlsx
+++ b/source/Hoyeh Menu May 26 -UPDATED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/om_hoyeh_jrgroup_com_sg/Documents/Desktop/menu-rws hoyeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="14_{29B8DDAB-B7B2-4575-AC21-864C4156FDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90A8453B-D9D2-4C70-A1AE-BB395E853199}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="14_{29B8DDAB-B7B2-4575-AC21-864C4156FDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCE20E71-A46D-4FAA-9534-4D6DB7776B7C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
@@ -2534,6 +2534,33 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2544,33 +2571,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3136,7 +3136,7 @@
         <v>372</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="H9" s="23" t="s">
         <v>40</v>
@@ -3162,8 +3162,8 @@
       <c r="F10" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>514</v>
+      <c r="G10" s="20" t="s">
+        <v>526</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>466</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3201,7 +3201,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="93"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="19" t="s">
         <v>281</v>
       </c>
@@ -3226,7 +3226,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="93"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="66" t="s">
         <v>467</v>
       </c>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="93"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="19" t="s">
         <v>82</v>
       </c>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="93"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3301,7 +3301,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="94"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3406,7 +3406,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="87" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3462,8 +3462,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3489,8 +3489,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88"/>
-      <c r="B23" s="93"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="31" t="s">
         <v>473</v>
       </c>
@@ -3514,8 +3514,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88"/>
-      <c r="B24" s="93"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="31" t="s">
         <v>78</v>
       </c>
@@ -3539,8 +3539,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="88"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="19" t="s">
         <v>314</v>
       </c>
@@ -3564,8 +3564,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88"/>
-      <c r="B26" s="93"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="19" t="s">
         <v>116</v>
       </c>
@@ -3589,8 +3589,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="88"/>
-      <c r="B27" s="94"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -3614,7 +3614,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -3641,7 +3641,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3668,7 +3668,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -3695,7 +3695,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3724,7 +3724,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3751,8 +3751,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3778,8 +3778,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>281</v>
       </c>
@@ -3803,8 +3803,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>82</v>
       </c>
@@ -3828,8 +3828,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3853,8 +3853,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3878,7 +3878,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -3905,7 +3905,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -4412,8 +4412,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
       <c r="C3" s="68">
         <v>46153</v>
       </c>
@@ -4631,7 +4631,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4658,7 +4658,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="19" t="s">
         <v>102</v>
       </c>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="19" t="s">
         <v>332</v>
       </c>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="19" t="s">
         <v>105</v>
       </c>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="19" t="s">
         <v>109</v>
       </c>
@@ -4758,7 +4758,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="19" t="s">
         <v>235</v>
       </c>
@@ -4863,7 +4863,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -4892,7 +4892,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -4919,8 +4919,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4946,8 +4946,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="19" t="s">
         <v>112</v>
       </c>
@@ -4971,8 +4971,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88"/>
-      <c r="B24" s="85"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="94"/>
       <c r="C24" s="19" t="s">
         <v>353</v>
       </c>
@@ -4996,8 +4996,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="88"/>
-      <c r="B25" s="85"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="19" t="s">
         <v>237</v>
       </c>
@@ -5021,8 +5021,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="66" t="s">
         <v>236</v>
       </c>
@@ -5046,8 +5046,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="88"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="19" t="s">
         <v>25</v>
       </c>
@@ -5071,7 +5071,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -5098,7 +5098,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -5125,7 +5125,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -5152,7 +5152,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="62" t="s">
@@ -5181,7 +5181,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="63" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5208,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="84" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5235,8 +5235,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91"/>
-      <c r="B34" s="85"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="94"/>
       <c r="C34" s="19" t="s">
         <v>102</v>
       </c>
@@ -5260,8 +5260,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="85"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="19" t="s">
         <v>105</v>
       </c>
@@ -5285,8 +5285,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91"/>
-      <c r="B36" s="85"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="19" t="s">
         <v>109</v>
       </c>
@@ -5310,8 +5310,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
-      <c r="B37" s="85"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="94"/>
       <c r="C37" s="19" t="s">
         <v>235</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="63" t="s">
         <v>59</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="63" t="s">
         <v>13</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="63" t="s">
         <v>60</v>
       </c>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6113,7 +6113,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="93"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="31" t="s">
         <v>373</v>
       </c>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="93"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="31" t="s">
         <v>379</v>
       </c>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="93"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="31" t="s">
         <v>390</v>
       </c>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="93"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="31" t="s">
         <v>395</v>
       </c>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="94"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="31" t="s">
         <v>142</v>
       </c>
@@ -6318,7 +6318,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6347,7 +6347,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6374,8 +6374,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6401,8 +6401,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88"/>
-      <c r="B23" s="93"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="31" t="s">
         <v>148</v>
       </c>
@@ -6426,8 +6426,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88"/>
-      <c r="B24" s="93"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6451,8 +6451,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="88"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="85"/>
       <c r="C25" s="31" t="s">
         <v>415</v>
       </c>
@@ -6476,8 +6476,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88"/>
-      <c r="B26" s="93"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="85"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6501,8 +6501,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="88"/>
-      <c r="B27" s="94"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="86"/>
       <c r="C27" s="31" t="s">
         <v>369</v>
       </c>
@@ -6526,7 +6526,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="17" t="s">
         <v>59</v>
       </c>
@@ -6553,7 +6553,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6580,7 +6580,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="38" t="s">
         <v>60</v>
       </c>
@@ -6607,7 +6607,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6636,7 +6636,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6663,8 +6663,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6690,8 +6690,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="31" t="s">
         <v>373</v>
       </c>
@@ -6715,8 +6715,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="31" t="s">
         <v>390</v>
       </c>
@@ -6740,8 +6740,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="31" t="s">
         <v>395</v>
       </c>
@@ -6765,8 +6765,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="31" t="s">
         <v>142</v>
       </c>
@@ -6790,7 +6790,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -6817,7 +6817,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6844,7 +6844,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
@@ -7530,7 +7530,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="82"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -7557,7 +7557,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82"/>
-      <c r="B12" s="85"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="19" t="s">
         <v>168</v>
       </c>
@@ -7582,7 +7582,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="82"/>
-      <c r="B13" s="85"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="19" t="s">
         <v>434</v>
       </c>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82"/>
-      <c r="B14" s="85"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="19" t="s">
         <v>251</v>
       </c>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="82"/>
-      <c r="B15" s="85"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="19" t="s">
         <v>250</v>
       </c>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
-      <c r="B16" s="86"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="19" t="s">
         <v>502</v>
       </c>
@@ -7762,7 +7762,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="96" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="62" t="s">
@@ -7791,7 +7791,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="88"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="63" t="s">
         <v>43</v>
       </c>
@@ -7818,8 +7818,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="87"/>
+      <c r="B22" s="93" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7845,8 +7845,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="19" t="s">
         <v>175</v>
       </c>
@@ -7870,8 +7870,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88"/>
-      <c r="B24" s="85"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="94"/>
       <c r="C24" s="19" t="s">
         <v>179</v>
       </c>
@@ -7895,8 +7895,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="88"/>
-      <c r="B25" s="85"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="19" t="s">
         <v>105</v>
       </c>
@@ -7920,8 +7920,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="19" t="s">
         <v>260</v>
       </c>
@@ -7945,8 +7945,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="88"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="19" t="s">
         <v>455</v>
       </c>
@@ -7970,7 +7970,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="63" t="s">
         <v>59</v>
       </c>
@@ -7997,7 +7997,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="88"/>
+      <c r="A29" s="87"/>
       <c r="B29" s="63" t="s">
         <v>13</v>
       </c>
@@ -8024,7 +8024,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="64" t="s">
         <v>60</v>
       </c>
@@ -8051,7 +8051,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8080,7 +8080,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="91"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8107,8 +8107,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="91"/>
-      <c r="B33" s="92" t="s">
+      <c r="A33" s="90"/>
+      <c r="B33" s="84" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -8134,8 +8134,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="91"/>
-      <c r="B34" s="93"/>
+      <c r="A34" s="90"/>
+      <c r="B34" s="85"/>
       <c r="C34" s="19" t="s">
         <v>168</v>
       </c>
@@ -8159,8 +8159,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="91"/>
-      <c r="B35" s="93"/>
+      <c r="A35" s="90"/>
+      <c r="B35" s="85"/>
       <c r="C35" s="19" t="s">
         <v>251</v>
       </c>
@@ -8184,8 +8184,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="91"/>
-      <c r="B36" s="93"/>
+      <c r="A36" s="90"/>
+      <c r="B36" s="85"/>
       <c r="C36" s="19" t="s">
         <v>250</v>
       </c>
@@ -8209,8 +8209,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
-      <c r="B37" s="93"/>
+      <c r="A37" s="90"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="19" t="s">
         <v>502</v>
       </c>
@@ -8234,7 +8234,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="17" t="s">
         <v>59</v>
       </c>
@@ -8261,7 +8261,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8288,7 +8288,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="91"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="17" t="s">
         <v>60</v>
       </c>
